--- a/data/Supplementary_Tables.xlsx
+++ b/data/Supplementary_Tables.xlsx
@@ -18,6 +18,7 @@
     <sheet name="S6" sheetId="9" r:id="rId9"/>
     <sheet name="S6b" sheetId="10" r:id="rId10"/>
     <sheet name="S7" sheetId="11" r:id="rId11"/>
+    <sheet name="S8" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -361,7 +362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -493,6 +494,18 @@
       <c r="B11" t="inlineStr">
         <is>
           <t>Mean Kbhb-TMR activity (NES) per TMR, per Cohort x de novo cluster block (the same 4 blocks split in Figure 1C).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Editor-requested addition (IJMS Minor Revision round 2): contingency counts (cluster x histologic grade, per cohort). TCGA grade derived from Thennavan et al. 2021 Data S2 (Cell Genomics 1:100067, PMID 35465400); METABRIC grade from clinical annotation. Fisher exact test (Monte Carlo p, BH-adjusted, independent 2-test family -- see data/basal_denovo_cluster_vs_grade.tsv) reported in Results/Methods.</t>
         </is>
       </c>
     </row>
@@ -1681,6 +1694,254 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Freq</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TCGA: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TCGA: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TCGA: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TCGA: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TCGA: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TCGA: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>METABRIC: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>METABRIC: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>METABRIC: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>METABRIC: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>METABRIC: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>METABRIC: de novo cluster vs Grade</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M171"/>
